--- a/optimized_uipath/Config.xlsx
+++ b/optimized_uipath/Config.xlsx
@@ -36,12 +36,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">D:\WorkBuddy-WorkSpace\invoice-automation\invoices_input</t>
+          <t xml:space="preserve">..\invoices_input</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">发票收件箱：机器人扫描这个目录</t>
+          <t xml:space="preserve">发票收件箱：机器人扫描这个目录（相对 UiPath 工程目录，即仓库根的 invoices_input）</t>
         </is>
       </c>
     </row>
@@ -53,12 +53,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">D:\WorkBuddy-WorkSpace\invoice-automation\optimized_uipath\output</t>
+          <t xml:space="preserve">output</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">输出目录：台账 / 报告 / 待复核清单都写在这里</t>
+          <t xml:space="preserve">输出目录：台账 / 报告 / 待复核清单都写在这里（相对 UiPath 工程目录）</t>
         </is>
       </c>
     </row>
@@ -70,7 +70,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">D:\WorkBuddy-WorkSpace\invoice-automation\optimized_uipath\output\_processed</t>
+          <t xml:space="preserve">output\_processed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -87,7 +87,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">D:\WorkBuddy-WorkSpace\invoice-automation\optimized_uipath\output\_failed</t>
+          <t xml:space="preserve">output\_failed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
